--- a/DATA/DGPMV COMERCIALES.xlsx
+++ b/DATA/DGPMV COMERCIALES.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bf48b3f04032ef9d/Documentos/SERVICIOS/PARKA/MIGRACIÓN/OFICINA/ALEX/IA-NAMI/BASES/DATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5295188-AC36-46DA-B1D4-82292C74E0AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{C5295188-AC36-46DA-B1D4-82292C74E0AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AFC79C2-1999-4CF1-BF95-084DD8123584}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="5265" windowWidth="29040" windowHeight="15720" xr2:uid="{3EB34577-2607-43E8-A848-732DECC94A0B}"/>
+    <workbookView xWindow="43080" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3EB34577-2607-43E8-A848-732DECC94A0B}"/>
   </bookViews>
   <sheets>
     <sheet name="COMERCIALES" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">COMERCIALES!$A$1:$H$333</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="31">
   <si>
     <t>DIA</t>
   </si>
@@ -68,163 +71,70 @@
     <t xml:space="preserve">JALISCO </t>
   </si>
   <si>
-    <t xml:space="preserve">AEROPUERTO INTERNACIONAL DE GUADALAJARA </t>
-  </si>
-  <si>
     <t>QUINTANA ROO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AEROPUERTO INTERNACIONAL DE CANCÚN </t>
   </si>
   <si>
     <t>NUEVO LEÓN</t>
   </si>
   <si>
-    <t xml:space="preserve">AEROPUERTO INTERNACIONAL DE MONTERREY </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AEROPUERTO INTERNACIONAL DE PUERTO VALLARTA </t>
-  </si>
-  <si>
     <t xml:space="preserve">CDMX </t>
-  </si>
-  <si>
-    <t>AEROPUERTO INTERNACIONAL DE LA CIUDAD DE MÉXICO</t>
   </si>
   <si>
     <t xml:space="preserve">QUERETARO </t>
   </si>
   <si>
-    <t xml:space="preserve">AEROPUERTO INTERNACIONAL DE QUERETARO </t>
-  </si>
-  <si>
     <t>SONORA</t>
-  </si>
-  <si>
-    <t>AEROPUERTO INTERNACIONAL DE HERMOSILLO</t>
   </si>
   <si>
     <t xml:space="preserve">GUERRRERO </t>
   </si>
   <si>
-    <t xml:space="preserve">AEROPUERTO INTERNACIONAL DE ZIHUATANEJO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAJA CALIFORNIA SUR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AEROPUERTO INTERNACIONAL DE LOS CABOS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAJA CALIFORNIA  </t>
-  </si>
-  <si>
-    <t>BAJA CALIFORNIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SONORA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAJA CALIFORNIA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MICHOACAN </t>
-  </si>
-  <si>
-    <t>AEROPUERTO INTERNACIONAL DE MORELIA</t>
-  </si>
-  <si>
     <t>Jalisco</t>
-  </si>
-  <si>
-    <t>Aeropuerto Internacional de Guadalajara</t>
-  </si>
-  <si>
-    <t>Nuevo León</t>
-  </si>
-  <si>
-    <t>Aeropuerto Internacional de Monterrey</t>
-  </si>
-  <si>
-    <t>Baja California</t>
-  </si>
-  <si>
-    <t>Aeropuerto internacional de los Cabos</t>
-  </si>
-  <si>
-    <t>Quintana Roo</t>
-  </si>
-  <si>
-    <t>Aeropuerto Internacional de Cancún</t>
-  </si>
-  <si>
-    <t>Sonora</t>
-  </si>
-  <si>
-    <t>Aeropuerto Internacional de Hermosillo</t>
   </si>
   <si>
     <t>CDMX</t>
   </si>
   <si>
-    <t>Aeropuerto Internacional de Ciudad México</t>
-  </si>
-  <si>
-    <t>Michoacán</t>
-  </si>
-  <si>
-    <t>Aeropuerto internacional de Morelia</t>
-  </si>
-  <si>
-    <t>Aeropuerto Internacional de Puerto Vallarta</t>
-  </si>
-  <si>
-    <t>01.09.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AEROPUERTO INTERNACIONAL DE LA CIUDAD DE MEXICO </t>
-  </si>
-  <si>
-    <t>NUEVO LEON</t>
-  </si>
-  <si>
-    <t>AEROPUERTO INTERNACION DE MONTERREY</t>
-  </si>
-  <si>
-    <t>02.09.2026</t>
-  </si>
-  <si>
     <t>QUERETARO</t>
-  </si>
-  <si>
-    <t>AEROPUERTO INTERNACIONAL DE QUERETAEO</t>
   </si>
   <si>
     <t>JALISCO</t>
   </si>
   <si>
-    <t>AEROPUERTO INTERNACIONAL DE PUERTO VALLARTA</t>
+    <t>A. I de Guadalajara</t>
   </si>
   <si>
-    <t>AEROPUERTO INTERNACIONAL DE GUADALAJARA</t>
+    <t>A. I.  Cancún</t>
   </si>
   <si>
-    <t>03.09.2026</t>
+    <t>A. I de Monterrey</t>
   </si>
   <si>
-    <t>04.09.2026</t>
+    <t>A. I. Puerto Vallarta</t>
   </si>
   <si>
-    <t>AEROPUERTO INTERNACIONAL DE CANCUN</t>
+    <t>A. I. Ciudad de México</t>
   </si>
   <si>
-    <t>AEROPUERTOINTERNACIONAL DE LOS CABOS</t>
+    <t>A. I. de Queretaro</t>
   </si>
   <si>
-    <t>05.09.2026</t>
+    <t>A. I. Hermosillo</t>
   </si>
   <si>
-    <t>06.09.2026</t>
+    <t>A. I. Zihuatanejo</t>
+  </si>
+  <si>
+    <t>Baja California Sur</t>
+  </si>
+  <si>
+    <t>A. I. Los Cabos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICHOACÁN </t>
+  </si>
+  <si>
+    <t>A. I. Morelia</t>
   </si>
 </sst>
 </file>
@@ -355,7 +265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -384,6 +294,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -399,6 +315,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -698,7 +618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ACCA23C-A544-4229-A04A-EBDAAC4C3A19}">
-  <dimension ref="A1:H333"/>
+  <dimension ref="A1:H343"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.73046875" bestFit="1" customWidth="1"/>
@@ -743,8 +663,8 @@
       <c r="B2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>9</v>
+      <c r="C2" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D2" s="8">
         <v>2</v>
@@ -767,10 +687,10 @@
         <v>46156</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D3" s="8">
         <v>1</v>
@@ -793,10 +713,10 @@
         <v>46156</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D4" s="8">
         <v>4</v>
@@ -821,8 +741,8 @@
       <c r="B5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>9</v>
+      <c r="C5" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D5" s="7">
         <v>1</v>
@@ -845,10 +765,10 @@
         <v>46157</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D6" s="7">
         <v>1</v>
@@ -873,8 +793,8 @@
       <c r="B7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>9</v>
+      <c r="C7" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D7" s="7">
         <v>1</v>
@@ -897,10 +817,10 @@
         <v>46158</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D8" s="7">
         <v>2</v>
@@ -923,10 +843,10 @@
         <v>46159</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D9" s="7">
         <v>5</v>
@@ -949,10 +869,10 @@
         <v>46159</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D10" s="7">
         <v>4</v>
@@ -977,8 +897,8 @@
       <c r="B11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>9</v>
+      <c r="C11" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D11" s="7">
         <v>2</v>
@@ -1001,10 +921,10 @@
         <v>46160</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D12" s="7">
         <v>4</v>
@@ -1027,10 +947,10 @@
         <v>46161</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D13" s="7">
         <v>2</v>
@@ -1053,10 +973,10 @@
         <v>46161</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="7">
         <v>4</v>
@@ -1081,8 +1001,8 @@
       <c r="B15" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>9</v>
+      <c r="C15" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D15" s="7">
         <v>4</v>
@@ -1107,8 +1027,8 @@
       <c r="B16" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>14</v>
+      <c r="C16" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D16" s="7">
         <v>5</v>
@@ -1131,10 +1051,10 @@
         <v>46162</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D17" s="7">
         <v>11</v>
@@ -1157,10 +1077,10 @@
         <v>46162</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D18" s="7">
         <v>7</v>
@@ -1183,10 +1103,10 @@
         <v>46163</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="D19" s="7">
         <v>1</v>
@@ -1209,10 +1129,10 @@
         <v>46163</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D20" s="7">
         <v>4</v>
@@ -1235,10 +1155,10 @@
         <v>46163</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D21" s="7">
         <v>10</v>
@@ -1263,8 +1183,8 @@
       <c r="B22" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>9</v>
+      <c r="C22" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D22" s="7">
         <v>2</v>
@@ -1289,8 +1209,8 @@
       <c r="B23" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>14</v>
+      <c r="C23" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D23" s="7">
         <v>5</v>
@@ -1313,10 +1233,10 @@
         <v>46165</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D24" s="7">
         <v>2</v>
@@ -1339,10 +1259,10 @@
         <v>46166</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D25" s="7">
         <v>3</v>
@@ -1367,8 +1287,8 @@
       <c r="B26" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>14</v>
+      <c r="C26" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D26" s="7">
         <v>5</v>
@@ -1393,8 +1313,8 @@
       <c r="B27" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>9</v>
+      <c r="C27" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D27" s="7">
         <v>4</v>
@@ -1417,10 +1337,10 @@
         <v>46168</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="7">
         <v>5</v>
@@ -1445,8 +1365,8 @@
       <c r="B29" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="7" t="s">
-        <v>14</v>
+      <c r="C29" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D29" s="7">
         <v>1</v>
@@ -1471,8 +1391,8 @@
       <c r="B30" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C30" s="7" t="s">
-        <v>9</v>
+      <c r="C30" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D30" s="7">
         <v>3</v>
@@ -1495,10 +1415,10 @@
         <v>46169</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="7">
         <v>5</v>
@@ -1523,8 +1443,8 @@
       <c r="B32" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C32" s="7" t="s">
-        <v>14</v>
+      <c r="C32" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D32" s="7">
         <v>3</v>
@@ -1549,8 +1469,8 @@
       <c r="B33" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="7" t="s">
-        <v>9</v>
+      <c r="C33" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D33" s="7">
         <v>2</v>
@@ -1573,10 +1493,10 @@
         <v>46170</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D34" s="7">
         <v>1</v>
@@ -1599,10 +1519,10 @@
         <v>46170</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D35" s="7">
         <v>4</v>
@@ -1625,10 +1545,10 @@
         <v>46171</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="D36" s="7">
         <v>1</v>
@@ -1651,10 +1571,10 @@
         <v>46171</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D37" s="7">
         <v>7</v>
@@ -1679,8 +1599,8 @@
       <c r="B38" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C38" s="7" t="s">
-        <v>14</v>
+      <c r="C38" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D38" s="7">
         <v>4</v>
@@ -1703,10 +1623,10 @@
         <v>46171</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D39" s="7">
         <v>4</v>
@@ -1729,10 +1649,10 @@
         <v>46175</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="D40" s="7">
         <v>2</v>
@@ -1757,8 +1677,8 @@
       <c r="B41" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C41" s="7" t="s">
-        <v>14</v>
+      <c r="C41" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D41" s="7">
         <v>2</v>
@@ -1781,10 +1701,10 @@
         <v>46175</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D42" s="7">
         <v>2</v>
@@ -1807,10 +1727,10 @@
         <v>46176</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="D43" s="7">
         <v>5</v>
@@ -1833,10 +1753,10 @@
         <v>46176</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D44" s="7">
         <v>6</v>
@@ -1861,8 +1781,8 @@
       <c r="B45" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C45" s="7" t="s">
-        <v>9</v>
+      <c r="C45" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D45" s="7">
         <v>5</v>
@@ -1885,10 +1805,10 @@
         <v>46177</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D46" s="7">
         <v>6</v>
@@ -1913,8 +1833,8 @@
       <c r="B47" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="7" t="s">
-        <v>14</v>
+      <c r="C47" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D47" s="7">
         <v>4</v>
@@ -1939,8 +1859,8 @@
       <c r="B48" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C48" s="7" t="s">
-        <v>9</v>
+      <c r="C48" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D48" s="7">
         <v>2</v>
@@ -1963,10 +1883,10 @@
         <v>46178</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D49" s="7">
         <v>9</v>
@@ -1989,10 +1909,10 @@
         <v>46179</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D50" s="7">
         <v>5</v>
@@ -2017,8 +1937,8 @@
       <c r="B51" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="7" t="s">
-        <v>9</v>
+      <c r="C51" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D51" s="7">
         <v>4</v>
@@ -2041,10 +1961,10 @@
         <v>46180</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D52" s="7">
         <v>1</v>
@@ -2067,10 +1987,10 @@
         <v>46242</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="D53" s="7">
         <v>2</v>
@@ -2093,10 +2013,10 @@
         <v>46181</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D54" s="7">
         <v>6</v>
@@ -2119,10 +2039,10 @@
         <v>46182</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D55" s="7">
         <v>5</v>
@@ -2145,10 +2065,10 @@
         <v>46183</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D56" s="7">
         <v>3</v>
@@ -2171,10 +2091,10 @@
         <v>46184</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D57" s="7">
         <v>12</v>
@@ -2199,8 +2119,8 @@
       <c r="B58" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C58" s="7" t="s">
-        <v>9</v>
+      <c r="C58" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D58" s="7">
         <v>8</v>
@@ -2223,10 +2143,10 @@
         <v>46184</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D59" s="7">
         <v>1</v>
@@ -2249,10 +2169,10 @@
         <v>46185</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="D60" s="7">
         <v>2</v>
@@ -2275,10 +2195,10 @@
         <v>46185</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D61" s="7">
         <v>4</v>
@@ -2301,10 +2221,10 @@
         <v>46185</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D62" s="7">
         <v>4</v>
@@ -2329,8 +2249,8 @@
       <c r="B63" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C63" s="7" t="s">
-        <v>9</v>
+      <c r="C63" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D63" s="7">
         <v>4</v>
@@ -2353,10 +2273,10 @@
         <v>46186</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D64" s="7">
         <v>5</v>
@@ -2379,10 +2299,10 @@
         <v>46187</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D65" s="7">
         <v>5</v>
@@ -2405,10 +2325,10 @@
         <v>46188</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="D66" s="7">
         <v>4</v>
@@ -2431,10 +2351,10 @@
         <v>46188</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D67" s="7">
         <v>2</v>
@@ -2459,8 +2379,8 @@
       <c r="B68" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C68" s="7" t="s">
-        <v>9</v>
+      <c r="C68" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D68" s="7">
         <v>3</v>
@@ -2483,10 +2403,10 @@
         <v>46188</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D69" s="7">
         <v>6</v>
@@ -2509,10 +2429,10 @@
         <v>46189</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D70" s="7">
         <v>10</v>
@@ -2535,10 +2455,10 @@
         <v>46189</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="D71" s="7">
         <v>4</v>
@@ -2563,8 +2483,8 @@
       <c r="B72" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C72" s="7" t="s">
-        <v>9</v>
+      <c r="C72" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D72" s="7">
         <v>7</v>
@@ -2587,10 +2507,10 @@
         <v>46190</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D73" s="7">
         <v>1</v>
@@ -2615,8 +2535,8 @@
       <c r="B74" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C74" s="7" t="s">
-        <v>9</v>
+      <c r="C74" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D74" s="7">
         <v>4</v>
@@ -2639,10 +2559,10 @@
         <v>46190</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D75" s="7">
         <v>6</v>
@@ -2665,10 +2585,10 @@
         <v>46191</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D76" s="7">
         <v>4</v>
@@ -2693,8 +2613,8 @@
       <c r="B77" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C77" s="7" t="s">
-        <v>9</v>
+      <c r="C77" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D77" s="7">
         <v>3</v>
@@ -2719,8 +2639,8 @@
       <c r="B78" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C78" s="7" t="s">
-        <v>9</v>
+      <c r="C78" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D78" s="7">
         <v>4</v>
@@ -2743,10 +2663,10 @@
         <v>46193</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>22</v>
+        <v>14</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>26</v>
       </c>
       <c r="D79" s="7">
         <v>1</v>
@@ -2769,10 +2689,10 @@
         <v>46193</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D80" s="7">
         <v>3</v>
@@ -2797,8 +2717,8 @@
       <c r="B81" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C81" s="7" t="s">
-        <v>9</v>
+      <c r="C81" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D81" s="7">
         <v>7</v>
@@ -2821,10 +2741,10 @@
         <v>46193</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D82" s="7">
         <v>1</v>
@@ -2847,10 +2767,10 @@
         <v>46193</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D83" s="7">
         <v>3</v>
@@ -2875,8 +2795,8 @@
       <c r="B84" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C84" s="7" t="s">
-        <v>9</v>
+      <c r="C84" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D84" s="7">
         <v>7</v>
@@ -2899,10 +2819,10 @@
         <v>46194</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C85" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D85" s="7">
         <v>3</v>
@@ -2927,8 +2847,8 @@
       <c r="B86" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C86" s="7" t="s">
-        <v>9</v>
+      <c r="C86" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D86" s="7">
         <v>10</v>
@@ -2951,10 +2871,10 @@
         <v>46195</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D87" s="7">
         <v>7</v>
@@ -2977,10 +2897,10 @@
         <v>46195</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="C88" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D88" s="7">
         <v>3</v>
@@ -3003,10 +2923,10 @@
         <v>46196</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D89" s="7">
         <v>4</v>
@@ -3029,10 +2949,10 @@
         <v>46196</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="C90" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D90" s="7">
         <v>4</v>
@@ -3055,10 +2975,10 @@
         <v>46197</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D91" s="7">
         <v>8</v>
@@ -3083,8 +3003,8 @@
       <c r="B92" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C92" s="7" t="s">
-        <v>9</v>
+      <c r="C92" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D92" s="7">
         <v>7</v>
@@ -3107,10 +3027,10 @@
         <v>46197</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C93" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D93" s="7">
         <v>7</v>
@@ -3133,10 +3053,10 @@
         <v>46197</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D94" s="7">
         <v>2</v>
@@ -3159,10 +3079,10 @@
         <v>46198</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C95" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D95" s="7">
         <v>2</v>
@@ -3187,8 +3107,8 @@
       <c r="B96" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C96" s="7" t="s">
-        <v>9</v>
+      <c r="C96" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D96" s="7">
         <v>17</v>
@@ -3211,10 +3131,10 @@
         <v>46198</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D97" s="7">
         <v>12</v>
@@ -3237,10 +3157,10 @@
         <v>46198</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="C98" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D98" s="7">
         <v>4</v>
@@ -3263,10 +3183,10 @@
         <v>46199</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C99" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D99" s="7">
         <v>1</v>
@@ -3291,8 +3211,8 @@
       <c r="B100" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C100" s="7" t="s">
-        <v>9</v>
+      <c r="C100" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D100" s="7">
         <v>8</v>
@@ -3315,10 +3235,10 @@
         <v>46199</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C101" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D101" s="7">
         <v>1</v>
@@ -3341,10 +3261,10 @@
         <v>46199</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="C102" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D102" s="7">
         <v>4</v>
@@ -3367,10 +3287,10 @@
         <v>46200</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="C103" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D103" s="7">
         <v>3</v>
@@ -3395,8 +3315,8 @@
       <c r="B104" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C104" s="7" t="s">
-        <v>9</v>
+      <c r="C104" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D104" s="7">
         <v>14</v>
@@ -3419,10 +3339,10 @@
         <v>46201</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C105" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C105" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D105" s="7">
         <v>1</v>
@@ -3447,8 +3367,8 @@
       <c r="B106" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C106" s="7" t="s">
-        <v>9</v>
+      <c r="C106" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D106" s="7">
         <v>9</v>
@@ -3471,10 +3391,10 @@
         <v>46201</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="C107" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D107" s="7">
         <v>3</v>
@@ -3497,10 +3417,10 @@
         <v>46202</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C108" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D108" s="7">
         <v>1</v>
@@ -3525,8 +3445,8 @@
       <c r="B109" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C109" s="7" t="s">
-        <v>9</v>
+      <c r="C109" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D109" s="7">
         <v>19</v>
@@ -3549,10 +3469,10 @@
         <v>46203</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C110" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D110" s="7">
         <v>12</v>
@@ -3577,8 +3497,8 @@
       <c r="B111" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C111" s="7" t="s">
-        <v>9</v>
+      <c r="C111" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D111" s="7">
         <v>4</v>
@@ -3601,10 +3521,10 @@
         <v>46203</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C112" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C112" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D112" s="7">
         <v>4</v>
@@ -3627,10 +3547,10 @@
         <v>46203</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C113" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="C113" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D113" s="7">
         <v>3</v>
@@ -3653,10 +3573,10 @@
         <v>46204</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C114" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C114" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D114" s="7">
         <v>4</v>
@@ -3679,10 +3599,10 @@
         <v>46204</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C115" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="C115" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D115" s="7">
         <v>2</v>
@@ -3707,8 +3627,8 @@
       <c r="B116" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C116" s="7" t="s">
-        <v>9</v>
+      <c r="C116" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D116" s="7">
         <v>9</v>
@@ -3731,10 +3651,10 @@
         <v>46204</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C117" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C117" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D117" s="7">
         <v>1</v>
@@ -3757,10 +3677,10 @@
         <v>46204</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C118" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="C118" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D118" s="7">
         <v>6</v>
@@ -3783,10 +3703,10 @@
         <v>46205</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C119" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D119" s="7">
         <v>5</v>
@@ -3809,10 +3729,10 @@
         <v>46205</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C120" s="7" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="C120" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="D120" s="7">
         <v>5</v>
@@ -3835,10 +3755,10 @@
         <v>46205</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C121" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="C121" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D121" s="7">
         <v>5</v>
@@ -3863,8 +3783,8 @@
       <c r="B122" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C122" s="7" t="s">
-        <v>9</v>
+      <c r="C122" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D122" s="7">
         <v>6</v>
@@ -3887,10 +3807,10 @@
         <v>46205</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C123" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="C123" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D123" s="7">
         <v>3</v>
@@ -3913,10 +3833,10 @@
         <v>46206</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C124" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C124" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D124" s="7">
         <v>4</v>
@@ -3939,10 +3859,10 @@
         <v>46206</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C125" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="C125" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D125" s="7">
         <v>5</v>
@@ -3967,8 +3887,8 @@
       <c r="B126" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C126" s="7" t="s">
-        <v>9</v>
+      <c r="C126" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D126" s="7">
         <v>11</v>
@@ -3991,10 +3911,10 @@
         <v>46206</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C127" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C127" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D127" s="7">
         <v>11</v>
@@ -4017,10 +3937,10 @@
         <v>46206</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C128" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="C128" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D128" s="7">
         <v>1</v>
@@ -4043,10 +3963,10 @@
         <v>46207</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C129" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C129" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D129" s="7">
         <v>5</v>
@@ -4071,8 +3991,8 @@
       <c r="B130" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C130" s="7" t="s">
-        <v>9</v>
+      <c r="C130" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D130" s="7">
         <v>11</v>
@@ -4095,10 +4015,10 @@
         <v>46207</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C131" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C131" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D131" s="7">
         <v>5</v>
@@ -4121,10 +4041,10 @@
         <v>46207</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C132" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="C132" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D132" s="7">
         <v>6</v>
@@ -4149,8 +4069,8 @@
       <c r="B133" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C133" s="7" t="s">
-        <v>9</v>
+      <c r="C133" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D133" s="7">
         <v>10</v>
@@ -4173,10 +4093,10 @@
         <v>46208</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C134" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C134" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D134" s="7">
         <v>3</v>
@@ -4201,8 +4121,8 @@
       <c r="B135" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C135" s="7" t="s">
-        <v>9</v>
+      <c r="C135" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D135" s="7">
         <v>6</v>
@@ -4225,10 +4145,10 @@
         <v>46209</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C136" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C136" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D136" s="7">
         <v>10</v>
@@ -4251,10 +4171,10 @@
         <v>46210</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C137" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C137" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D137" s="7">
         <v>6</v>
@@ -4279,8 +4199,8 @@
       <c r="B138" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C138" s="7" t="s">
-        <v>9</v>
+      <c r="C138" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D138" s="7">
         <v>2</v>
@@ -4303,10 +4223,10 @@
         <v>46210</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C139" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C139" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D139" s="7">
         <v>5</v>
@@ -4329,10 +4249,10 @@
         <v>46210</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C140" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="C140" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D140" s="7">
         <v>2</v>
@@ -4355,10 +4275,10 @@
         <v>46211</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C141" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="C141" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D141" s="7">
         <v>6</v>
@@ -4383,8 +4303,8 @@
       <c r="B142" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C142" s="7" t="s">
-        <v>9</v>
+      <c r="C142" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D142" s="7">
         <v>5</v>
@@ -4407,10 +4327,10 @@
         <v>46212</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C143" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="C143" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D143" s="7">
         <v>10</v>
@@ -4435,8 +4355,8 @@
       <c r="B144" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C144" s="7" t="s">
-        <v>9</v>
+      <c r="C144" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D144" s="7">
         <v>1</v>
@@ -4459,10 +4379,10 @@
         <v>46213</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C145" s="7" t="s">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="C145" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="D145" s="7">
         <v>1</v>
@@ -4487,8 +4407,8 @@
       <c r="B146" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C146" s="7" t="s">
-        <v>9</v>
+      <c r="C146" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D146" s="7">
         <v>11</v>
@@ -4511,10 +4431,10 @@
         <v>46213</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C147" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C147" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D147" s="7">
         <v>4</v>
@@ -4537,10 +4457,10 @@
         <v>46213</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C148" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="C148" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D148" s="7">
         <v>4</v>
@@ -4563,10 +4483,10 @@
         <v>46214</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C149" s="7" t="s">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="C149" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="D149" s="7">
         <v>1</v>
@@ -4591,8 +4511,8 @@
       <c r="B150" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C150" s="7" t="s">
-        <v>9</v>
+      <c r="C150" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D150" s="7">
         <v>7</v>
@@ -4615,10 +4535,10 @@
         <v>46215</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C151" s="7" t="s">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="C151" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="D151" s="7">
         <v>1</v>
@@ -4641,10 +4561,10 @@
         <v>46215</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C152" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="C152" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D152" s="7">
         <v>2</v>
@@ -4667,10 +4587,10 @@
         <v>46216</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C153" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
+      </c>
+      <c r="C153" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="D153" s="7">
         <v>1</v>
@@ -4693,10 +4613,10 @@
         <v>46216</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C154" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="C154" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D154" s="7">
         <v>2</v>
@@ -4721,8 +4641,8 @@
       <c r="B155" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C155" s="7" t="s">
-        <v>9</v>
+      <c r="C155" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D155" s="7">
         <v>14</v>
@@ -4745,10 +4665,10 @@
         <v>46216</v>
       </c>
       <c r="B156" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C156" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="C156" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="D156" s="7">
         <v>7</v>
@@ -4771,10 +4691,10 @@
         <v>46217</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C157" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C157" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D157" s="7">
         <v>2</v>
@@ -4797,10 +4717,10 @@
         <v>46217</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C158" s="7" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="C158" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="D158" s="7">
         <v>6</v>
@@ -4825,8 +4745,8 @@
       <c r="B159" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C159" s="7" t="s">
-        <v>9</v>
+      <c r="C159" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D159" s="7">
         <v>7</v>
@@ -4849,10 +4769,10 @@
         <v>46218</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C160" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C160" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D160" s="7">
         <v>2</v>
@@ -4877,8 +4797,8 @@
       <c r="B161" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C161" s="7" t="s">
-        <v>9</v>
+      <c r="C161" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D161" s="7">
         <v>10</v>
@@ -4901,10 +4821,10 @@
         <v>46218</v>
       </c>
       <c r="B162" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C162" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="C162" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="D162" s="7">
         <v>4</v>
@@ -4927,10 +4847,10 @@
         <v>46219</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C163" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="C163" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D163" s="7">
         <v>3</v>
@@ -4955,8 +4875,8 @@
       <c r="B164" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C164" s="7" t="s">
-        <v>9</v>
+      <c r="C164" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D164" s="7">
         <v>12</v>
@@ -4979,10 +4899,10 @@
         <v>46219</v>
       </c>
       <c r="B165" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C165" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="C165" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="D165" s="7">
         <v>2</v>
@@ -5005,10 +4925,10 @@
         <v>46220</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C166" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="C166" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D166" s="7">
         <v>2</v>
@@ -5033,8 +4953,8 @@
       <c r="B167" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C167" s="7" t="s">
-        <v>9</v>
+      <c r="C167" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D167" s="7">
         <v>14</v>
@@ -5057,10 +4977,10 @@
         <v>46220</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C168" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C168" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D168" s="7">
         <v>3</v>
@@ -5083,10 +5003,10 @@
         <v>46220</v>
       </c>
       <c r="B169" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C169" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="C169" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="D169" s="7">
         <v>2</v>
@@ -5109,10 +5029,10 @@
         <v>46221</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C170" s="7" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="C170" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="D170" s="7">
         <v>6</v>
@@ -5137,8 +5057,8 @@
       <c r="B171" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C171" s="7" t="s">
-        <v>9</v>
+      <c r="C171" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D171" s="7">
         <v>10</v>
@@ -5161,10 +5081,10 @@
         <v>46221</v>
       </c>
       <c r="B172" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C172" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="C172" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="D172" s="7">
         <v>2</v>
@@ -5187,10 +5107,10 @@
         <v>46222</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C173" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C173" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D173" s="7">
         <v>1</v>
@@ -5213,10 +5133,10 @@
         <v>46222</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C174" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C174" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D174" s="7">
         <v>4</v>
@@ -5241,8 +5161,8 @@
       <c r="B175" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C175" s="7" t="s">
-        <v>9</v>
+      <c r="C175" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D175" s="7">
         <v>6</v>
@@ -5265,10 +5185,10 @@
         <v>46223</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C176" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C176" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D176" s="7">
         <v>4</v>
@@ -5291,10 +5211,10 @@
         <v>46223</v>
       </c>
       <c r="B177" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C177" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="C177" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="D177" s="7">
         <v>3</v>
@@ -5317,10 +5237,10 @@
         <v>46224</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C178" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C178" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D178" s="7">
         <v>2</v>
@@ -5345,8 +5265,8 @@
       <c r="B179" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C179" s="7" t="s">
-        <v>9</v>
+      <c r="C179" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D179" s="7">
         <v>2</v>
@@ -5369,10 +5289,10 @@
         <v>46224</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C180" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C180" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D180" s="7">
         <v>12</v>
@@ -5395,10 +5315,10 @@
         <v>46225</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C181" s="7" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="C181" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="D181" s="7">
         <v>7</v>
@@ -5421,10 +5341,10 @@
         <v>46225</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C182" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="C182" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D182" s="7">
         <v>2</v>
@@ -5449,8 +5369,8 @@
       <c r="B183" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C183" s="7" t="s">
-        <v>9</v>
+      <c r="C183" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D183" s="7">
         <v>11</v>
@@ -5470,13 +5390,13 @@
     </row>
     <row r="184" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A184" s="6">
-        <v>45495</v>
+        <v>46225</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C184" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C184" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D184" s="7">
         <v>3</v>
@@ -5499,10 +5419,10 @@
         <v>46225</v>
       </c>
       <c r="B185" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C185" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="C185" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="D185" s="7">
         <v>3</v>
@@ -5525,10 +5445,10 @@
         <v>46226</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C186" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C186" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D186" s="7">
         <v>1</v>
@@ -5551,10 +5471,10 @@
         <v>46226</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C187" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="C187" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D187" s="7">
         <v>1</v>
@@ -5579,8 +5499,8 @@
       <c r="B188" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C188" s="7" t="s">
-        <v>9</v>
+      <c r="C188" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D188" s="7">
         <v>10</v>
@@ -5603,10 +5523,10 @@
         <v>46226</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C189" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C189" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D189" s="7">
         <v>6</v>
@@ -5629,10 +5549,10 @@
         <v>46226</v>
       </c>
       <c r="B190" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C190" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="C190" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="D190" s="7">
         <v>3</v>
@@ -5654,10 +5574,10 @@
       <c r="A191" s="6">
         <v>46227</v>
       </c>
-      <c r="B191" s="7" t="s">
+      <c r="B191" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C191" s="7" t="s">
+      <c r="C191" s="10" t="s">
         <v>30</v>
       </c>
       <c r="D191" s="7">
@@ -5681,10 +5601,10 @@
         <v>46227</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C192" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="C192" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D192" s="7">
         <v>3</v>
@@ -5709,8 +5629,8 @@
       <c r="B193" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C193" s="7" t="s">
-        <v>9</v>
+      <c r="C193" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D193" s="7">
         <v>5</v>
@@ -5733,10 +5653,10 @@
         <v>46227</v>
       </c>
       <c r="B194" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C194" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="C194" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="D194" s="7">
         <v>4</v>
@@ -5759,10 +5679,10 @@
         <v>46228</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C195" s="7" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="C195" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="D195" s="7">
         <v>6</v>
@@ -5787,8 +5707,8 @@
       <c r="B196" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C196" s="7" t="s">
-        <v>9</v>
+      <c r="C196" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D196" s="7">
         <v>6</v>
@@ -5811,10 +5731,10 @@
         <v>46228</v>
       </c>
       <c r="B197" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C197" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="C197" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="D197" s="7">
         <v>2</v>
@@ -5837,10 +5757,10 @@
         <v>46229</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C198" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C198" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D198" s="7">
         <v>1</v>
@@ -5865,8 +5785,8 @@
       <c r="B199" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C199" s="7" t="s">
-        <v>9</v>
+      <c r="C199" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D199" s="7">
         <v>7</v>
@@ -5889,10 +5809,10 @@
         <v>46230</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C200" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C200" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D200" s="7">
         <v>4</v>
@@ -5915,10 +5835,10 @@
         <v>46230</v>
       </c>
       <c r="B201" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C201" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="C201" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="D201" s="7">
         <v>3</v>
@@ -5941,10 +5861,10 @@
         <v>46231</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C202" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C202" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D202" s="7">
         <v>6</v>
@@ -5969,8 +5889,8 @@
       <c r="B203" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C203" s="7" t="s">
-        <v>9</v>
+      <c r="C203" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D203" s="7">
         <v>6</v>
@@ -5995,8 +5915,8 @@
       <c r="B204" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C204" s="7" t="s">
-        <v>9</v>
+      <c r="C204" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D204" s="7">
         <v>3</v>
@@ -6019,10 +5939,10 @@
         <v>46232</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C205" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C205" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D205" s="7">
         <v>3</v>
@@ -6045,10 +5965,10 @@
         <v>46232</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C206" s="7" t="s">
-        <v>24</v>
+        <v>9</v>
+      </c>
+      <c r="C206" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D206" s="7">
         <v>3</v>
@@ -6071,10 +5991,10 @@
         <v>46233</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C207" s="7" t="s">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="C207" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="D207" s="7">
         <v>4</v>
@@ -6097,10 +6017,10 @@
         <v>46233</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C208" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C208" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D208" s="7">
         <v>6</v>
@@ -6125,8 +6045,8 @@
       <c r="B209" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C209" s="7" t="s">
-        <v>9</v>
+      <c r="C209" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D209" s="7">
         <v>2</v>
@@ -6149,10 +6069,10 @@
         <v>46233</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C210" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C210" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D210" s="7">
         <v>12</v>
@@ -6175,10 +6095,10 @@
         <v>46233</v>
       </c>
       <c r="B211" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C211" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="C211" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="D211" s="7">
         <v>3</v>
@@ -6201,10 +6121,10 @@
         <v>46234</v>
       </c>
       <c r="B212" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C212" s="7" t="s">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="C212" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="D212" s="7">
         <v>1</v>
@@ -6229,8 +6149,8 @@
       <c r="B213" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C213" s="7" t="s">
-        <v>9</v>
+      <c r="C213" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D213" s="7">
         <v>5</v>
@@ -6253,10 +6173,10 @@
         <v>46234</v>
       </c>
       <c r="B214" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C214" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C214" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D214" s="7">
         <v>4</v>
@@ -6279,10 +6199,10 @@
         <v>46234</v>
       </c>
       <c r="B215" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C215" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="C215" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="D215" s="7">
         <v>10</v>
@@ -6305,10 +6225,10 @@
         <v>46235</v>
       </c>
       <c r="B216" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C216" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C216" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D216" s="7">
         <v>8</v>
@@ -6331,10 +6251,10 @@
         <v>46235</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C217" s="7" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C217" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D217" s="7">
         <v>4</v>
@@ -6357,10 +6277,10 @@
         <v>46235</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C218" s="7" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="C218" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D218" s="7">
         <v>1</v>
@@ -6383,10 +6303,10 @@
         <v>46236</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C219" s="7" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C219" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D219" s="7">
         <v>5</v>
@@ -6409,10 +6329,10 @@
         <v>46237</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C220" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C220" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D220" s="7">
         <v>4</v>
@@ -6435,10 +6355,10 @@
         <v>46237</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C221" s="7" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C221" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D221" s="7">
         <v>13</v>
@@ -6461,10 +6381,10 @@
         <v>46237</v>
       </c>
       <c r="B222" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C222" s="7" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="C222" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D222" s="7">
         <v>2</v>
@@ -6487,10 +6407,10 @@
         <v>46238</v>
       </c>
       <c r="B223" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C223" s="7" t="s">
-        <v>38</v>
+        <v>9</v>
+      </c>
+      <c r="C223" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D223" s="7">
         <v>4</v>
@@ -6513,10 +6433,10 @@
         <v>46238</v>
       </c>
       <c r="B224" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C224" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C224" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D224" s="7">
         <v>9</v>
@@ -6539,10 +6459,10 @@
         <v>46239</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C225" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C225" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D225" s="7">
         <v>6</v>
@@ -6565,10 +6485,10 @@
         <v>46240</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C226" s="7" t="s">
-        <v>38</v>
+        <v>9</v>
+      </c>
+      <c r="C226" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D226" s="7">
         <v>5</v>
@@ -6591,10 +6511,10 @@
         <v>46240</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C227" s="7" t="s">
-        <v>40</v>
+        <v>13</v>
+      </c>
+      <c r="C227" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="D227" s="7">
         <v>5</v>
@@ -6617,10 +6537,10 @@
         <v>46240</v>
       </c>
       <c r="B228" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C228" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C228" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D228" s="7">
         <v>2</v>
@@ -6643,10 +6563,10 @@
         <v>46240</v>
       </c>
       <c r="B229" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C229" s="7" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C229" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D229" s="7">
         <v>5</v>
@@ -6669,10 +6589,10 @@
         <v>46240</v>
       </c>
       <c r="B230" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C230" s="7" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="C230" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D230" s="7">
         <v>2</v>
@@ -6695,10 +6615,10 @@
         <v>46241</v>
       </c>
       <c r="B231" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C231" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C231" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D231" s="7">
         <v>16</v>
@@ -6721,10 +6641,10 @@
         <v>46241</v>
       </c>
       <c r="B232" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C232" s="7" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C232" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D232" s="7">
         <v>7</v>
@@ -6747,10 +6667,10 @@
         <v>46242</v>
       </c>
       <c r="B233" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C233" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C233" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D233" s="7">
         <v>3</v>
@@ -6773,10 +6693,10 @@
         <v>46242</v>
       </c>
       <c r="B234" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C234" s="7" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C234" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D234" s="7">
         <v>4</v>
@@ -6799,10 +6719,10 @@
         <v>46242</v>
       </c>
       <c r="B235" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C235" s="7" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="C235" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D235" s="7">
         <v>7</v>
@@ -6825,10 +6745,10 @@
         <v>46243</v>
       </c>
       <c r="B236" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C236" s="7" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C236" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D236" s="7">
         <v>5</v>
@@ -6851,10 +6771,10 @@
         <v>46243</v>
       </c>
       <c r="B237" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C237" s="7" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="C237" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D237" s="7">
         <v>2</v>
@@ -6877,10 +6797,10 @@
         <v>46244</v>
       </c>
       <c r="B238" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C238" s="7" t="s">
-        <v>40</v>
+        <v>13</v>
+      </c>
+      <c r="C238" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="D238" s="7">
         <v>1</v>
@@ -6903,10 +6823,10 @@
         <v>46244</v>
       </c>
       <c r="B239" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C239" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C239" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D239" s="7">
         <v>6</v>
@@ -6929,10 +6849,10 @@
         <v>46244</v>
       </c>
       <c r="B240" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C240" s="7" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C240" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D240" s="7">
         <v>13</v>
@@ -6955,10 +6875,10 @@
         <v>46244</v>
       </c>
       <c r="B241" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C241" s="7" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="C241" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D241" s="7">
         <v>2</v>
@@ -6981,10 +6901,10 @@
         <v>46245</v>
       </c>
       <c r="B242" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C242" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C242" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D242" s="7">
         <v>5</v>
@@ -7007,10 +6927,10 @@
         <v>46246</v>
       </c>
       <c r="B243" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C243" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C243" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D243" s="7">
         <v>11</v>
@@ -7033,10 +6953,10 @@
         <v>46247</v>
       </c>
       <c r="B244" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C244" s="7" t="s">
-        <v>42</v>
+        <v>16</v>
+      </c>
+      <c r="C244" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="D244" s="7">
         <v>9</v>
@@ -7059,10 +6979,10 @@
         <v>46247</v>
       </c>
       <c r="B245" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C245" s="7" t="s">
-        <v>40</v>
+        <v>13</v>
+      </c>
+      <c r="C245" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="D245" s="7">
         <v>4</v>
@@ -7085,10 +7005,10 @@
         <v>46247</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C246" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C246" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D246" s="7">
         <v>8</v>
@@ -7111,10 +7031,10 @@
         <v>46248</v>
       </c>
       <c r="B247" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C247" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C247" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D247" s="7">
         <v>4</v>
@@ -7137,10 +7057,10 @@
         <v>46248</v>
       </c>
       <c r="B248" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C248" s="7" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C248" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D248" s="7">
         <v>14</v>
@@ -7163,10 +7083,10 @@
         <v>46248</v>
       </c>
       <c r="B249" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C249" s="7" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="C249" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D249" s="7">
         <v>3</v>
@@ -7189,10 +7109,10 @@
         <v>46249</v>
       </c>
       <c r="B250" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C250" s="7" t="s">
-        <v>40</v>
+        <v>13</v>
+      </c>
+      <c r="C250" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="D250" s="7">
         <v>5</v>
@@ -7215,10 +7135,10 @@
         <v>46249</v>
       </c>
       <c r="B251" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C251" s="7" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C251" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D251" s="7">
         <v>5</v>
@@ -7241,10 +7161,10 @@
         <v>46249</v>
       </c>
       <c r="B252" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C252" s="7" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="C252" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D252" s="7">
         <v>5</v>
@@ -7267,10 +7187,10 @@
         <v>46250</v>
       </c>
       <c r="B253" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C253" s="7" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C253" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D253" s="7">
         <v>5</v>
@@ -7293,10 +7213,10 @@
         <v>46251</v>
       </c>
       <c r="B254" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C254" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C254" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D254" s="7">
         <v>2</v>
@@ -7319,10 +7239,10 @@
         <v>46251</v>
       </c>
       <c r="B255" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C255" s="7" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C255" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D255" s="7">
         <v>8</v>
@@ -7345,10 +7265,10 @@
         <v>46251</v>
       </c>
       <c r="B256" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C256" s="7" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="C256" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D256" s="7">
         <v>5</v>
@@ -7371,10 +7291,10 @@
         <v>46252</v>
       </c>
       <c r="B257" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C257" s="7" t="s">
-        <v>38</v>
+        <v>9</v>
+      </c>
+      <c r="C257" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D257" s="7">
         <v>3</v>
@@ -7397,10 +7317,10 @@
         <v>46252</v>
       </c>
       <c r="B258" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C258" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C258" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D258" s="7">
         <v>2</v>
@@ -7423,10 +7343,10 @@
         <v>46252</v>
       </c>
       <c r="B259" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C259" s="7" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C259" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D259" s="7">
         <v>3</v>
@@ -7449,10 +7369,10 @@
         <v>46253</v>
       </c>
       <c r="B260" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C260" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C260" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D260" s="7">
         <v>5</v>
@@ -7475,10 +7395,10 @@
         <v>46254</v>
       </c>
       <c r="B261" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C261" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C261" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D261" s="7">
         <v>5</v>
@@ -7501,10 +7421,10 @@
         <v>46254</v>
       </c>
       <c r="B262" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C262" s="7" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C262" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D262" s="7">
         <v>10</v>
@@ -7527,10 +7447,10 @@
         <v>46254</v>
       </c>
       <c r="B263" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C263" s="7" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="C263" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D263" s="7">
         <v>2</v>
@@ -7553,10 +7473,10 @@
         <v>46255</v>
       </c>
       <c r="B264" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C264" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C264" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D264" s="7">
         <v>13</v>
@@ -7579,10 +7499,10 @@
         <v>46255</v>
       </c>
       <c r="B265" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C265" s="7" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="C265" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D265" s="7">
         <v>1</v>
@@ -7605,10 +7525,10 @@
         <v>46256</v>
       </c>
       <c r="B266" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C266" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C266" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D266" s="7">
         <v>2</v>
@@ -7631,10 +7551,10 @@
         <v>46256</v>
       </c>
       <c r="B267" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C267" s="7" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="C267" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D267" s="7">
         <v>9</v>
@@ -7657,10 +7577,10 @@
         <v>46257</v>
       </c>
       <c r="B268" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C268" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C268" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D268" s="7">
         <v>2</v>
@@ -7683,10 +7603,10 @@
         <v>46257</v>
       </c>
       <c r="B269" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C269" s="7" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="C269" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D269" s="7">
         <v>2</v>
@@ -7708,11 +7628,11 @@
       <c r="A270" s="6">
         <v>46258</v>
       </c>
-      <c r="B270" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C270" s="7" t="s">
-        <v>44</v>
+      <c r="B270" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C270" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="D270" s="7">
         <v>1</v>
@@ -7735,10 +7655,10 @@
         <v>46258</v>
       </c>
       <c r="B271" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C271" s="7" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C271" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D271" s="7">
         <v>9</v>
@@ -7761,10 +7681,10 @@
         <v>46258</v>
       </c>
       <c r="B272" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C272" s="7" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="C272" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D272" s="7">
         <v>5</v>
@@ -7787,10 +7707,10 @@
         <v>46259</v>
       </c>
       <c r="B273" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C273" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C273" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D273" s="7">
         <v>7</v>
@@ -7813,10 +7733,10 @@
         <v>46259</v>
       </c>
       <c r="B274" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C274" s="7" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C274" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D274" s="7">
         <v>3</v>
@@ -7839,10 +7759,10 @@
         <v>46260</v>
       </c>
       <c r="B275" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C275" s="7" t="s">
-        <v>45</v>
+        <v>18</v>
+      </c>
+      <c r="C275" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D275" s="7">
         <v>2</v>
@@ -7865,10 +7785,10 @@
         <v>46260</v>
       </c>
       <c r="B276" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C276" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C276" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D276" s="7">
         <v>7</v>
@@ -7891,10 +7811,10 @@
         <v>46261</v>
       </c>
       <c r="B277" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C277" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C277" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D277" s="7">
         <v>11</v>
@@ -7917,10 +7837,10 @@
         <v>46261</v>
       </c>
       <c r="B278" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C278" s="7" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C278" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D278" s="7">
         <v>10</v>
@@ -7943,10 +7863,10 @@
         <v>46261</v>
       </c>
       <c r="B279" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C279" s="7" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="C279" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D279" s="7">
         <v>1</v>
@@ -7969,10 +7889,10 @@
         <v>46262</v>
       </c>
       <c r="B280" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C280" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C280" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D280" s="7">
         <v>8</v>
@@ -7995,10 +7915,10 @@
         <v>46262</v>
       </c>
       <c r="B281" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C281" s="7" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C281" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D281" s="7">
         <v>15</v>
@@ -8021,10 +7941,10 @@
         <v>46263</v>
       </c>
       <c r="B282" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C282" s="7" t="s">
-        <v>40</v>
+        <v>13</v>
+      </c>
+      <c r="C282" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="D282" s="7">
         <v>5</v>
@@ -8047,10 +7967,10 @@
         <v>46263</v>
       </c>
       <c r="B283" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C283" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C283" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D283" s="7">
         <v>6</v>
@@ -8073,10 +7993,10 @@
         <v>46263</v>
       </c>
       <c r="B284" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C284" s="7" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C284" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D284" s="7">
         <v>7</v>
@@ -8099,10 +8019,10 @@
         <v>46263</v>
       </c>
       <c r="B285" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C285" s="7" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="C285" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D285" s="7">
         <v>5</v>
@@ -8125,10 +8045,10 @@
         <v>46264</v>
       </c>
       <c r="B286" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C286" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="C286" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D286" s="7">
         <v>2</v>
@@ -8151,10 +8071,10 @@
         <v>46265</v>
       </c>
       <c r="B287" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C287" s="7" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C287" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D287" s="7">
         <v>5</v>
@@ -8177,10 +8097,10 @@
         <v>46265</v>
       </c>
       <c r="B288" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C288" s="7" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="C288" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D288" s="7">
         <v>1</v>
@@ -8199,14 +8119,14 @@
       </c>
     </row>
     <row r="289" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A289" s="6" t="s">
-        <v>46</v>
+      <c r="A289" s="6">
+        <v>46266</v>
       </c>
       <c r="B289" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C289" s="7" t="s">
-        <v>47</v>
+        <v>16</v>
+      </c>
+      <c r="C289" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="D289" s="7">
         <v>1</v>
@@ -8225,14 +8145,14 @@
       </c>
     </row>
     <row r="290" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A290" s="6" t="s">
-        <v>46</v>
+      <c r="A290" s="6">
+        <v>46266</v>
       </c>
       <c r="B290" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C290" s="7" t="s">
-        <v>49</v>
+        <v>10</v>
+      </c>
+      <c r="C290" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D290" s="7">
         <v>5</v>
@@ -8251,14 +8171,14 @@
       </c>
     </row>
     <row r="291" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A291" s="6" t="s">
-        <v>50</v>
+      <c r="A291" s="6">
+        <v>46267</v>
       </c>
       <c r="B291" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C291" s="7" t="s">
-        <v>52</v>
+        <v>17</v>
+      </c>
+      <c r="C291" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="D291" s="7">
         <v>2</v>
@@ -8277,14 +8197,14 @@
       </c>
     </row>
     <row r="292" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A292" s="6" t="s">
-        <v>50</v>
+      <c r="A292" s="6">
+        <v>46267</v>
       </c>
       <c r="B292" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C292" s="7" t="s">
-        <v>54</v>
+        <v>18</v>
+      </c>
+      <c r="C292" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D292" s="7">
         <v>6</v>
@@ -8303,14 +8223,14 @@
       </c>
     </row>
     <row r="293" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A293" s="6" t="s">
-        <v>50</v>
+      <c r="A293" s="6">
+        <v>46267</v>
       </c>
       <c r="B293" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C293" s="7" t="s">
-        <v>55</v>
+        <v>18</v>
+      </c>
+      <c r="C293" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D293" s="7">
         <v>6</v>
@@ -8329,14 +8249,14 @@
       </c>
     </row>
     <row r="294" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A294" s="6" t="s">
-        <v>56</v>
+      <c r="A294" s="6">
+        <v>46268</v>
       </c>
       <c r="B294" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C294" s="7" t="s">
-        <v>54</v>
+        <v>18</v>
+      </c>
+      <c r="C294" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D294" s="7">
         <v>4</v>
@@ -8355,14 +8275,14 @@
       </c>
     </row>
     <row r="295" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A295" s="6" t="s">
-        <v>56</v>
+      <c r="A295" s="6">
+        <v>46268</v>
       </c>
       <c r="B295" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C295" s="7" t="s">
-        <v>55</v>
+        <v>18</v>
+      </c>
+      <c r="C295" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D295" s="7">
         <v>4</v>
@@ -8381,14 +8301,14 @@
       </c>
     </row>
     <row r="296" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A296" s="6" t="s">
-        <v>56</v>
+      <c r="A296" s="6">
+        <v>46268</v>
       </c>
       <c r="B296" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C296" s="7" t="s">
-        <v>49</v>
+        <v>10</v>
+      </c>
+      <c r="C296" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D296" s="7">
         <v>7</v>
@@ -8407,14 +8327,14 @@
       </c>
     </row>
     <row r="297" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A297" s="6" t="s">
-        <v>57</v>
+      <c r="A297" s="6">
+        <v>46269</v>
       </c>
       <c r="B297" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C297" s="7" t="s">
-        <v>58</v>
+        <v>9</v>
+      </c>
+      <c r="C297" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D297" s="7">
         <v>3</v>
@@ -8433,14 +8353,14 @@
       </c>
     </row>
     <row r="298" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A298" s="6" t="s">
-        <v>57</v>
+      <c r="A298" s="6">
+        <v>46269</v>
       </c>
       <c r="B298" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C298" s="7" t="s">
-        <v>55</v>
+        <v>18</v>
+      </c>
+      <c r="C298" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D298" s="7">
         <v>10</v>
@@ -8459,14 +8379,14 @@
       </c>
     </row>
     <row r="299" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A299" s="6" t="s">
-        <v>57</v>
+      <c r="A299" s="6">
+        <v>46269</v>
       </c>
       <c r="B299" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C299" s="7" t="s">
-        <v>49</v>
+        <v>10</v>
+      </c>
+      <c r="C299" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D299" s="7">
         <v>6</v>
@@ -8485,14 +8405,14 @@
       </c>
     </row>
     <row r="300" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A300" s="6" t="s">
-        <v>57</v>
+      <c r="A300" s="6">
+        <v>46269</v>
       </c>
       <c r="B300" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C300" s="7" t="s">
-        <v>59</v>
+        <v>27</v>
+      </c>
+      <c r="C300" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D300" s="7">
         <v>3</v>
@@ -8511,14 +8431,14 @@
       </c>
     </row>
     <row r="301" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A301" s="6" t="s">
-        <v>60</v>
+      <c r="A301" s="6">
+        <v>46270</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C301" s="7" t="s">
-        <v>47</v>
+        <v>16</v>
+      </c>
+      <c r="C301" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="D301" s="7">
         <v>2</v>
@@ -8537,14 +8457,14 @@
       </c>
     </row>
     <row r="302" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A302" s="6" t="s">
-        <v>60</v>
+      <c r="A302" s="6">
+        <v>46270</v>
       </c>
       <c r="B302" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C302" s="7" t="s">
-        <v>58</v>
+        <v>9</v>
+      </c>
+      <c r="C302" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D302" s="7">
         <v>3</v>
@@ -8563,14 +8483,14 @@
       </c>
     </row>
     <row r="303" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A303" s="6" t="s">
-        <v>60</v>
+      <c r="A303" s="6">
+        <v>46270</v>
       </c>
       <c r="B303" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C303" s="7" t="s">
-        <v>54</v>
+        <v>18</v>
+      </c>
+      <c r="C303" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D303" s="7">
         <v>1</v>
@@ -8589,14 +8509,14 @@
       </c>
     </row>
     <row r="304" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A304" s="6" t="s">
-        <v>60</v>
+      <c r="A304" s="6">
+        <v>46270</v>
       </c>
       <c r="B304" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C304" s="7" t="s">
-        <v>49</v>
+        <v>10</v>
+      </c>
+      <c r="C304" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D304" s="7">
         <v>6</v>
@@ -8615,14 +8535,14 @@
       </c>
     </row>
     <row r="305" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A305" s="6" t="s">
-        <v>61</v>
+      <c r="A305" s="6">
+        <v>46271</v>
       </c>
       <c r="B305" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C305" s="7" t="s">
-        <v>54</v>
+        <v>18</v>
+      </c>
+      <c r="C305" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D305" s="7">
         <v>3</v>
@@ -8642,13 +8562,13 @@
     </row>
     <row r="306" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A306" s="6">
-        <v>46637</v>
+        <v>46272</v>
       </c>
       <c r="B306" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C306" s="7" t="s">
-        <v>55</v>
+        <v>18</v>
+      </c>
+      <c r="C306" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D306" s="9">
         <v>5</v>
@@ -8668,13 +8588,13 @@
     </row>
     <row r="307" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A307" s="6">
-        <v>46637</v>
+        <v>46272</v>
       </c>
       <c r="B307" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C307" s="7" t="s">
-        <v>59</v>
+        <v>27</v>
+      </c>
+      <c r="C307" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D307" s="9">
         <v>6</v>
@@ -8694,13 +8614,13 @@
     </row>
     <row r="308" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A308" s="6">
-        <v>46638</v>
+        <v>46273</v>
       </c>
       <c r="B308" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C308" s="7" t="s">
-        <v>47</v>
+        <v>16</v>
+      </c>
+      <c r="C308" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="D308" s="9">
         <v>1</v>
@@ -8720,13 +8640,13 @@
     </row>
     <row r="309" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A309" s="6">
-        <v>46638</v>
+        <v>46273</v>
       </c>
       <c r="B309" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C309" s="7" t="s">
-        <v>55</v>
+        <v>18</v>
+      </c>
+      <c r="C309" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D309" s="9">
         <v>6</v>
@@ -8746,13 +8666,13 @@
     </row>
     <row r="310" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A310" s="6">
-        <v>46638</v>
+        <v>46273</v>
       </c>
       <c r="B310" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C310" s="7" t="s">
-        <v>49</v>
+        <v>10</v>
+      </c>
+      <c r="C310" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D310" s="9">
         <v>4</v>
@@ -8772,13 +8692,13 @@
     </row>
     <row r="311" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A311" s="6">
-        <v>46638</v>
+        <v>46273</v>
       </c>
       <c r="B311" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C311" s="7" t="s">
-        <v>59</v>
+        <v>27</v>
+      </c>
+      <c r="C311" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D311" s="9">
         <v>2</v>
@@ -8798,13 +8718,13 @@
     </row>
     <row r="312" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A312" s="6">
-        <v>46639</v>
+        <v>46274</v>
       </c>
       <c r="B312" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C312" s="7" t="s">
-        <v>58</v>
+        <v>9</v>
+      </c>
+      <c r="C312" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D312" s="9">
         <v>3</v>
@@ -8824,13 +8744,13 @@
     </row>
     <row r="313" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A313" s="6">
-        <v>46639</v>
+        <v>46274</v>
       </c>
       <c r="B313" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C313" s="7" t="s">
-        <v>54</v>
+        <v>18</v>
+      </c>
+      <c r="C313" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D313" s="9">
         <v>4</v>
@@ -8850,13 +8770,13 @@
     </row>
     <row r="314" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A314" s="6">
-        <v>46639</v>
+        <v>46274</v>
       </c>
       <c r="B314" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C314" s="7" t="s">
-        <v>55</v>
+        <v>18</v>
+      </c>
+      <c r="C314" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D314" s="9">
         <v>3</v>
@@ -8876,13 +8796,13 @@
     </row>
     <row r="315" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A315" s="6">
-        <v>46639</v>
+        <v>46274</v>
       </c>
       <c r="B315" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C315" s="7" t="s">
-        <v>59</v>
+        <v>27</v>
+      </c>
+      <c r="C315" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D315" s="9">
         <v>1</v>
@@ -8902,13 +8822,13 @@
     </row>
     <row r="316" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A316" s="6">
-        <v>46640</v>
+        <v>46275</v>
       </c>
       <c r="B316" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C316" s="7" t="s">
-        <v>52</v>
+        <v>17</v>
+      </c>
+      <c r="C316" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="D316" s="9">
         <v>2</v>
@@ -8928,13 +8848,13 @@
     </row>
     <row r="317" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A317" s="6">
-        <v>46640</v>
+        <v>46275</v>
       </c>
       <c r="B317" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C317" s="7" t="s">
-        <v>54</v>
+        <v>18</v>
+      </c>
+      <c r="C317" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D317" s="9">
         <v>3</v>
@@ -8954,13 +8874,13 @@
     </row>
     <row r="318" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A318" s="6">
-        <v>46640</v>
+        <v>46275</v>
       </c>
       <c r="B318" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C318" s="7" t="s">
-        <v>55</v>
+        <v>18</v>
+      </c>
+      <c r="C318" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D318" s="9">
         <v>1</v>
@@ -8980,13 +8900,13 @@
     </row>
     <row r="319" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A319" s="6">
-        <v>46640</v>
+        <v>46275</v>
       </c>
       <c r="B319" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C319" s="7" t="s">
-        <v>49</v>
+        <v>10</v>
+      </c>
+      <c r="C319" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D319" s="9">
         <v>1</v>
@@ -9006,13 +8926,13 @@
     </row>
     <row r="320" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A320" s="6">
-        <v>46640</v>
+        <v>46275</v>
       </c>
       <c r="B320" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C320" s="7" t="s">
-        <v>59</v>
+        <v>27</v>
+      </c>
+      <c r="C320" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D320" s="9">
         <v>3</v>
@@ -9032,13 +8952,13 @@
     </row>
     <row r="321" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A321" s="6">
-        <v>46641</v>
+        <v>46276</v>
       </c>
       <c r="B321" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C321" s="7" t="s">
-        <v>58</v>
+        <v>9</v>
+      </c>
+      <c r="C321" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D321" s="9">
         <v>4</v>
@@ -9058,13 +8978,13 @@
     </row>
     <row r="322" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A322" s="6">
-        <v>46641</v>
+        <v>46276</v>
       </c>
       <c r="B322" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C322" s="7" t="s">
-        <v>55</v>
+        <v>18</v>
+      </c>
+      <c r="C322" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D322" s="9">
         <v>2</v>
@@ -9084,13 +9004,13 @@
     </row>
     <row r="323" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A323" s="6">
-        <v>46641</v>
+        <v>46276</v>
       </c>
       <c r="B323" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C323" s="7" t="s">
-        <v>59</v>
+        <v>27</v>
+      </c>
+      <c r="C323" s="10" t="s">
+        <v>28</v>
       </c>
       <c r="D323" s="9">
         <v>4</v>
@@ -9110,13 +9030,13 @@
     </row>
     <row r="324" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A324" s="6">
-        <v>46642</v>
+        <v>46277</v>
       </c>
       <c r="B324" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C324" s="7" t="s">
-        <v>49</v>
+        <v>10</v>
+      </c>
+      <c r="C324" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D324" s="9">
         <v>2</v>
@@ -9136,13 +9056,13 @@
     </row>
     <row r="325" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A325" s="6">
-        <v>46643</v>
+        <v>46278</v>
       </c>
       <c r="B325" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C325" s="7" t="s">
-        <v>49</v>
+        <v>10</v>
+      </c>
+      <c r="C325" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D325" s="9">
         <v>1</v>
@@ -9162,13 +9082,13 @@
     </row>
     <row r="326" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A326" s="6">
-        <v>46644</v>
+        <v>46279</v>
       </c>
       <c r="B326" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C326" s="7" t="s">
-        <v>49</v>
+        <v>10</v>
+      </c>
+      <c r="C326" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D326" s="9">
         <v>5</v>
@@ -9188,13 +9108,13 @@
     </row>
     <row r="327" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A327" s="6">
-        <v>46645</v>
+        <v>46280</v>
       </c>
       <c r="B327" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C327" s="7" t="s">
-        <v>58</v>
+        <v>9</v>
+      </c>
+      <c r="C327" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D327" s="9">
         <v>1</v>
@@ -9214,13 +9134,13 @@
     </row>
     <row r="328" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A328" s="6">
-        <v>46645</v>
+        <v>46280</v>
       </c>
       <c r="B328" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C328" s="7" t="s">
-        <v>55</v>
+        <v>18</v>
+      </c>
+      <c r="C328" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="D328" s="9">
         <v>1</v>
@@ -9240,13 +9160,13 @@
     </row>
     <row r="329" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A329" s="6">
-        <v>46648</v>
+        <v>46283</v>
       </c>
       <c r="B329" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C329" s="7" t="s">
-        <v>49</v>
+        <v>10</v>
+      </c>
+      <c r="C329" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D329" s="9">
         <v>4</v>
@@ -9266,13 +9186,13 @@
     </row>
     <row r="330" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A330" s="6">
-        <v>46649</v>
+        <v>46284</v>
       </c>
       <c r="B330" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C330" s="7" t="s">
-        <v>58</v>
+        <v>9</v>
+      </c>
+      <c r="C330" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D330" s="9">
         <v>4</v>
@@ -9292,13 +9212,13 @@
     </row>
     <row r="331" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A331" s="6">
-        <v>46649</v>
+        <v>46284</v>
       </c>
       <c r="B331" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C331" s="7" t="s">
-        <v>49</v>
+        <v>10</v>
+      </c>
+      <c r="C331" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D331" s="9">
         <v>4</v>
@@ -9318,13 +9238,13 @@
     </row>
     <row r="332" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A332" s="6">
-        <v>46650</v>
+        <v>46285</v>
       </c>
       <c r="B332" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C332" s="7" t="s">
-        <v>58</v>
+        <v>9</v>
+      </c>
+      <c r="C332" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="D332" s="9">
         <v>6</v>
@@ -9344,13 +9264,13 @@
     </row>
     <row r="333" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A333" s="6">
-        <v>46650</v>
+        <v>46285</v>
       </c>
       <c r="B333" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C333" s="7" t="s">
-        <v>49</v>
+        <v>10</v>
+      </c>
+      <c r="C333" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="D333" s="9">
         <v>1</v>
@@ -9365,6 +9285,266 @@
         <v>0</v>
       </c>
       <c r="H333" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A334" s="6">
+        <v>46286</v>
+      </c>
+      <c r="B334" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C334" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D334" s="9">
+        <v>7</v>
+      </c>
+      <c r="E334" s="9">
+        <v>7</v>
+      </c>
+      <c r="F334" s="9">
+        <v>0</v>
+      </c>
+      <c r="G334" s="9">
+        <v>0</v>
+      </c>
+      <c r="H334" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A335" s="6">
+        <v>46286</v>
+      </c>
+      <c r="B335" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C335" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D335" s="9">
+        <v>2</v>
+      </c>
+      <c r="E335" s="9">
+        <v>2</v>
+      </c>
+      <c r="F335" s="9">
+        <v>0</v>
+      </c>
+      <c r="G335" s="9">
+        <v>0</v>
+      </c>
+      <c r="H335" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A336" s="6">
+        <v>46287</v>
+      </c>
+      <c r="B336" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C336" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D336" s="9">
+        <v>1</v>
+      </c>
+      <c r="E336" s="9">
+        <v>1</v>
+      </c>
+      <c r="F336" s="9">
+        <v>0</v>
+      </c>
+      <c r="G336" s="9">
+        <v>0</v>
+      </c>
+      <c r="H336" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A337" s="6">
+        <v>46287</v>
+      </c>
+      <c r="B337" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C337" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D337" s="9">
+        <v>3</v>
+      </c>
+      <c r="E337" s="9">
+        <v>3</v>
+      </c>
+      <c r="F337" s="9">
+        <v>0</v>
+      </c>
+      <c r="G337" s="9">
+        <v>0</v>
+      </c>
+      <c r="H337" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A338" s="6">
+        <v>46288</v>
+      </c>
+      <c r="B338" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C338" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D338" s="9">
+        <v>6</v>
+      </c>
+      <c r="E338" s="9">
+        <v>6</v>
+      </c>
+      <c r="F338" s="9">
+        <v>0</v>
+      </c>
+      <c r="G338" s="9">
+        <v>0</v>
+      </c>
+      <c r="H338" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A339" s="6">
+        <v>46289</v>
+      </c>
+      <c r="B339" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C339" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D339" s="9">
+        <v>1</v>
+      </c>
+      <c r="E339" s="9">
+        <v>1</v>
+      </c>
+      <c r="F339" s="9">
+        <v>0</v>
+      </c>
+      <c r="G339" s="9">
+        <v>0</v>
+      </c>
+      <c r="H339" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A340" s="6">
+        <v>46290</v>
+      </c>
+      <c r="B340" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C340" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D340" s="9">
+        <v>4</v>
+      </c>
+      <c r="E340" s="9">
+        <v>4</v>
+      </c>
+      <c r="F340" s="9">
+        <v>0</v>
+      </c>
+      <c r="G340" s="9">
+        <v>0</v>
+      </c>
+      <c r="H340" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A341" s="6">
+        <v>46291</v>
+      </c>
+      <c r="B341" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C341" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D341" s="9">
+        <v>2</v>
+      </c>
+      <c r="E341" s="9">
+        <v>2</v>
+      </c>
+      <c r="F341" s="9">
+        <v>0</v>
+      </c>
+      <c r="G341" s="9">
+        <v>0</v>
+      </c>
+      <c r="H341" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A342" s="6">
+        <v>46293</v>
+      </c>
+      <c r="B342" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C342" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D342" s="9">
+        <v>1</v>
+      </c>
+      <c r="E342" s="9">
+        <v>1</v>
+      </c>
+      <c r="F342" s="9">
+        <v>0</v>
+      </c>
+      <c r="G342" s="9">
+        <v>0</v>
+      </c>
+      <c r="H342" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A343" s="6">
+        <v>46293</v>
+      </c>
+      <c r="B343" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C343" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D343" s="9">
+        <v>7</v>
+      </c>
+      <c r="E343" s="9">
+        <v>7</v>
+      </c>
+      <c r="F343" s="9">
+        <v>0</v>
+      </c>
+      <c r="G343" s="9">
+        <v>0</v>
+      </c>
+      <c r="H343" s="9">
         <v>0</v>
       </c>
     </row>
